--- a/Config/Excel/window.xlsx
+++ b/Config/Excel/window.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11655"/>
+    <workbookView windowWidth="29865" windowHeight="12735"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
   <si>
     <t>id</t>
   </si>
@@ -40,6 +40,9 @@
     <t>c</t>
   </si>
   <si>
+    <t>ss</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -49,13 +52,31 @@
     <t>xx</t>
   </si>
   <si>
+    <t>备注</t>
+  </si>
+  <si>
     <t>Assets/Bundles/UI/Window/Guide/WinGuide</t>
   </si>
   <si>
+    <t>引导界面</t>
+  </si>
+  <si>
     <t>Assets/Bundles/UI/Window/Login/WinLogin</t>
   </si>
   <si>
+    <t>登录界面</t>
+  </si>
+  <si>
     <t>Assets/Bundles/UI/Window/Overview/WinOverview</t>
+  </si>
+  <si>
+    <t>主界面</t>
+  </si>
+  <si>
+    <t>Assets/Bundles/UI/Window/Overview/Package/WinPackage</t>
+  </si>
+  <si>
+    <t>背包界面</t>
   </si>
 </sst>
 </file>
@@ -1023,10 +1044,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="1"/>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
-    <col min="2" max="2" width="46.375" customWidth="1"/>
+    <col min="2" max="2" width="54.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1037,52 +1058,91 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
       </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>100001</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>100002</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:3">
       <c r="A7">
         <v>100003</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>100004</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9">
+        <v>100005</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10">
+        <v>100006</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Excel/window.xlsx
+++ b/Config/Excel/window.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29865" windowHeight="12735"/>
+    <workbookView windowWidth="27945" windowHeight="11655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
   <si>
     <t>id</t>
   </si>
@@ -77,6 +77,12 @@
   </si>
   <si>
     <t>背包界面</t>
+  </si>
+  <si>
+    <t>Assets/Bundles/UI/Window/GM/WinGM</t>
+  </si>
+  <si>
+    <t>GM界面</t>
   </si>
 </sst>
 </file>
@@ -1135,9 +1141,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:3">
       <c r="A9">
         <v>100005</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:1">

--- a/Config/Excel/window.xlsx
+++ b/Config/Excel/window.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
   <si>
     <t>id</t>
   </si>
@@ -83,6 +83,12 @@
   </si>
   <si>
     <t>GM界面</t>
+  </si>
+  <si>
+    <t>Assets/Bundles/UI/Window/Fight/WinFightBg</t>
+  </si>
+  <si>
+    <t>战斗背景界面</t>
   </si>
 </sst>
 </file>
@@ -1152,9 +1158,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:3">
       <c r="A10">
         <v>100006</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Excel/window.xlsx
+++ b/Config/Excel/window.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11655"/>
+    <workbookView windowWidth="29865" windowHeight="12735"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -88,7 +88,7 @@
     <t>Assets/Bundles/UI/Window/Fight/WinFightBg</t>
   </si>
   <si>
-    <t>战斗背景界面</t>
+    <t>战斗基础界面</t>
   </si>
 </sst>
 </file>

--- a/Config/Excel/window.xlsx
+++ b/Config/Excel/window.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29865" windowHeight="12735"/>
+    <workbookView windowWidth="27945" windowHeight="11655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
   <si>
     <t>id</t>
   </si>
@@ -85,10 +85,28 @@
     <t>GM界面</t>
   </si>
   <si>
-    <t>Assets/Bundles/UI/Window/Fight/WinFightBg</t>
+    <t>Assets/Bundles/UI/Window/Battle/WinBattleBg</t>
   </si>
   <si>
     <t>战斗基础界面</t>
+  </si>
+  <si>
+    <t>Assets/Bundles/UI/Window/Battle/WinBattleAction</t>
+  </si>
+  <si>
+    <t>战斗行为界面1</t>
+  </si>
+  <si>
+    <t>Assets/Bundles/UI/Window/Battle/WinBattleAction2</t>
+  </si>
+  <si>
+    <t>战斗行为界面2</t>
+  </si>
+  <si>
+    <t>Assets/Bundles/UI/Window/Battle/WinBattleInfo</t>
+  </si>
+  <si>
+    <t>战斗信息界面</t>
   </si>
 </sst>
 </file>
@@ -1056,10 +1074,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="54.75" customWidth="1"/>
+    <col min="3" max="3" width="27.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1167,6 +1186,79 @@
       </c>
       <c r="C10" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11">
+        <v>100007</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12">
+        <v>100008</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13">
+        <v>100009</v>
+      </c>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14">
+        <v>100010</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15">
+        <v>100011</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16">
+        <v>100012</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17">
+        <v>100013</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18">
+        <v>100014</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19">
+        <v>100015</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20">
+        <v>100016</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21">
+        <v>100017</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Excel/window.xlsx
+++ b/Config/Excel/window.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11655"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
